--- a/Experiments data/Cardinality Skewness/Skewness_PGP_Graph.xlsx
+++ b/Experiments data/Cardinality Skewness/Skewness_PGP_Graph.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\SISR Script\Experiments data\Cardinality Skewness\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\KaMinPar_Java\Experiments data\Cardinality Skewness\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{365892D3-AA1E-4B2A-AEEA-DA995B3371D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A325CA-5DC5-4EEC-83F2-82A6A1A92A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edge Cuts" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="39">
   <si>
     <t>KaHIP</t>
   </si>
@@ -134,13 +134,25 @@
     <t>Partition Sizes = [4216, 2951, 2066, 1447]</t>
   </si>
   <si>
-    <t>Partition Sizes = [7539, 2262, 679, 203]</t>
-  </si>
-  <si>
     <t>Deep Multilevel, ε = 5</t>
   </si>
   <si>
     <t>Deep Multilevel, ε= 0</t>
+  </si>
+  <si>
+    <t>Deep Multilevel, ε = 534</t>
+  </si>
+  <si>
+    <t>Partition Sizes = [7539, 2260, 678, 203]</t>
+  </si>
+  <si>
+    <t>Deep Multilevel, ε = 100</t>
+  </si>
+  <si>
+    <t>Deep NUGP, ε= 0</t>
+  </si>
+  <si>
+    <t>Deep NUGP, ε = 534</t>
   </si>
 </sst>
 </file>
@@ -319,6 +331,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -340,7 +353,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -695,19 +707,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>2814</c:v>
+                  <c:v>765.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2006.6</c:v>
+                  <c:v>825.4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>913.6</c:v>
+                  <c:v>859.2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2675.2</c:v>
+                  <c:v>916</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2032</c:v>
+                  <c:v>670</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -728,7 +740,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 0.05</c:v>
+                  <c:v>Deep Multilevel, ε = 534</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -794,19 +806,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1810.4</c:v>
+                  <c:v>507.4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1117.5999999999999</c:v>
+                  <c:v>759.4</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>746</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1860.8</c:v>
+                  <c:v>671.2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2592.1999999999998</c:v>
+                  <c:v>599.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1767,7 +1779,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε= 0</c:v>
+                  <c:v>Deep NUGP, ε= 0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1827,19 +1839,19 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>-2.0680331443523765</c:v>
+                  <c:v>0.16572176188399476</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.93500482160077136</c:v>
+                  <c:v>0.20405014464802315</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.1632041122295925E-2</c:v>
+                  <c:v>7.9888627115013822E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-1.7785625259659326</c:v>
+                  <c:v>4.8608226007478141E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-1.1617021276595745</c:v>
+                  <c:v>0.28723404255319152</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1860,7 +1872,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 5</c:v>
+                  <c:v>Deep NUGP, ε = 534</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1920,19 +1932,19 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>-0.97383340601831658</c:v>
+                  <c:v>0.44679459223724383</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-7.7724204435872621E-2</c:v>
+                  <c:v>0.267695274831244</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.20111372884986076</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-0.93269630245118407</c:v>
+                  <c:v>0.3028666389696717</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-1.757659574468085</c:v>
+                  <c:v>0.36212765957446807</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2116,7 +2128,7 @@
                   <a:rPr lang="en-US" sz="1600" b="0" i="0" baseline="0">
                     <a:effectLst/>
                   </a:rPr>
-                  <a:t>Percentage of Decline</a:t>
+                  <a:t>Percentage of Improvement</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-US" sz="900">
                   <a:effectLst/>
@@ -2547,7 +2559,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε= 0</c:v>
+                  <c:v>Deep NUGP, ε= 0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2613,19 +2625,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>4.4578000000000007</c:v>
+                  <c:v>2.0491999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.2334000000000005</c:v>
+                  <c:v>2.4645999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>2.3188</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.4497999999999998</c:v>
+                  <c:v>3.2698</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.0120000000000005</c:v>
+                  <c:v>3.2920000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2646,7 +2658,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 5</c:v>
+                  <c:v>Deep NUGP, ε = 534</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2712,19 +2724,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>2.1663999999999999</c:v>
+                  <c:v>2.1360000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.8439999999999999</c:v>
+                  <c:v>2.3527999999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.5575999999999999</c:v>
+                  <c:v>2.5575999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.0835999999999997</c:v>
+                  <c:v>2.8836000000000004</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.0835999999999997</c:v>
+                  <c:v>2.8836000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3888,7 +3900,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 5</c:v>
+                  <c:v>Deep Multilevel, ε = 534</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3948,7 +3960,7 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>2.7252800000000001E-2</c:v>
+                  <c:v>4.9239999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>4.4242400000000001E-2</c:v>
@@ -4518,7 +4530,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε= 0</c:v>
+                  <c:v>Deep NUGP, ε= 0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4611,7 +4623,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 5</c:v>
+                  <c:v>Deep NUGP, ε = 534</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4671,19 +4683,19 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>2.5373999999999997E-2</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.4226000000000001E-2</c:v>
+                  <c:v>0.1197</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.1531999999999999E-2</c:v>
+                  <c:v>0.1012424</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.2878000000000006E-2</c:v>
+                  <c:v>0.13762959999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.4876000000000004E-2</c:v>
+                  <c:v>0.10664660000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10221,26 +10233,26 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
@@ -10266,7 +10278,7 @@
         <v>26</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -10292,10 +10304,10 @@
         <v>870</v>
       </c>
       <c r="H5">
-        <v>3667</v>
+        <v>933</v>
       </c>
       <c r="I5">
-        <v>1554</v>
+        <v>507</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -10321,10 +10333,10 @@
         <v>959</v>
       </c>
       <c r="H6">
-        <v>2672</v>
+        <v>746</v>
       </c>
       <c r="I6">
-        <v>1993</v>
+        <v>575</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -10350,10 +10362,10 @@
         <v>933</v>
       </c>
       <c r="H7">
-        <v>2905</v>
+        <v>739</v>
       </c>
       <c r="I7">
-        <v>1964</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -10379,10 +10391,10 @@
         <v>927</v>
       </c>
       <c r="H8">
-        <v>2035</v>
+        <v>644</v>
       </c>
       <c r="I8">
-        <v>1610</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -10408,10 +10420,10 @@
         <v>897</v>
       </c>
       <c r="H9">
-        <v>2791</v>
+        <v>764</v>
       </c>
       <c r="I9">
-        <v>1931</v>
+        <v>529</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -10423,26 +10435,26 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
     </row>
     <row r="17" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
@@ -10468,7 +10480,7 @@
         <v>26</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -10494,10 +10506,10 @@
         <v>939</v>
       </c>
       <c r="H18">
-        <v>1755</v>
+        <v>821</v>
       </c>
       <c r="I18">
-        <v>1024</v>
+        <v>764</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -10523,10 +10535,10 @@
         <v>880</v>
       </c>
       <c r="H19">
-        <v>2369</v>
+        <v>932</v>
       </c>
       <c r="I19">
-        <v>947</v>
+        <v>719</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -10552,10 +10564,10 @@
         <v>882</v>
       </c>
       <c r="H20">
-        <v>1977</v>
+        <v>869</v>
       </c>
       <c r="I20">
-        <v>1481</v>
+        <v>806</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -10581,10 +10593,10 @@
         <v>1064</v>
       </c>
       <c r="H21">
-        <v>1624</v>
+        <v>803</v>
       </c>
       <c r="I21">
-        <v>1065</v>
+        <v>747</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -10610,10 +10622,10 @@
         <v>1420</v>
       </c>
       <c r="H22">
-        <v>2308</v>
+        <v>702</v>
       </c>
       <c r="I22">
-        <v>1071</v>
+        <v>761</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -10625,26 +10637,26 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
     </row>
     <row r="30" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
@@ -10670,7 +10682,7 @@
         <v>26</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -10696,7 +10708,7 @@
         <v>968</v>
       </c>
       <c r="H31">
-        <v>935</v>
+        <v>840</v>
       </c>
       <c r="I31">
         <v>749</v>
@@ -10725,7 +10737,7 @@
         <v>857</v>
       </c>
       <c r="H32">
-        <v>1007</v>
+        <v>915</v>
       </c>
       <c r="I32">
         <v>739</v>
@@ -10812,7 +10824,7 @@
         <v>1158</v>
       </c>
       <c r="H35">
-        <v>992</v>
+        <v>907</v>
       </c>
       <c r="I35">
         <v>754</v>
@@ -10827,26 +10839,26 @@
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="13" t="s">
+      <c r="A41" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
+      <c r="A42" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
     </row>
     <row r="43" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
@@ -10872,7 +10884,7 @@
         <v>26</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -10898,10 +10910,10 @@
         <v>912</v>
       </c>
       <c r="H44">
-        <v>2559</v>
+        <v>947</v>
       </c>
       <c r="I44">
-        <v>2376</v>
+        <v>713</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -10927,10 +10939,10 @@
         <v>1007</v>
       </c>
       <c r="H45">
-        <v>2735</v>
+        <v>932</v>
       </c>
       <c r="I45">
-        <v>1977</v>
+        <v>632</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -10956,10 +10968,10 @@
         <v>954</v>
       </c>
       <c r="H46">
-        <v>2416</v>
+        <v>995</v>
       </c>
       <c r="I46">
-        <v>1761</v>
+        <v>702</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -10985,10 +10997,10 @@
         <v>898</v>
       </c>
       <c r="H47">
-        <v>3711</v>
+        <v>920</v>
       </c>
       <c r="I47">
-        <v>2004</v>
+        <v>614</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -11014,10 +11026,10 @@
         <v>1043</v>
       </c>
       <c r="H48">
-        <v>1955</v>
+        <v>786</v>
       </c>
       <c r="I48">
-        <v>1186</v>
+        <v>695</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -11025,30 +11037,30 @@
         <v>3</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="13" t="s">
+      <c r="A54" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B54" s="13"/>
-      <c r="C54" s="13"/>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
+      <c r="B54" s="14"/>
+      <c r="C54" s="14"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="14"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="12" t="s">
+      <c r="A55" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B55" s="12"/>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
     </row>
     <row r="56" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
@@ -11074,7 +11086,7 @@
         <v>26</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
@@ -11100,10 +11112,10 @@
         <v>922</v>
       </c>
       <c r="H57">
-        <v>2194</v>
+        <v>768</v>
       </c>
       <c r="I57">
-        <v>2706</v>
+        <v>597</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -11129,10 +11141,10 @@
         <v>955</v>
       </c>
       <c r="H58">
-        <v>3323</v>
+        <v>606</v>
       </c>
       <c r="I58">
-        <v>2226</v>
+        <v>604</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
@@ -11158,10 +11170,10 @@
         <v>944</v>
       </c>
       <c r="H59">
-        <v>1636</v>
+        <v>680</v>
       </c>
       <c r="I59">
-        <v>2958</v>
+        <v>588</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -11187,10 +11199,10 @@
         <v>953</v>
       </c>
       <c r="H60">
-        <v>1997</v>
+        <v>536</v>
       </c>
       <c r="I60">
-        <v>2692</v>
+        <v>595</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
@@ -11216,33 +11228,33 @@
         <v>926</v>
       </c>
       <c r="H61">
-        <v>1010</v>
+        <v>760</v>
       </c>
       <c r="I61">
-        <v>2379</v>
+        <v>614</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A65" s="14" t="s">
+      <c r="A65" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
+      <c r="B65" s="15"/>
+      <c r="C65" s="15"/>
+      <c r="D65" s="15"/>
+      <c r="E65" s="15"/>
+      <c r="F65" s="15"/>
+      <c r="G65" s="15"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A66" s="12" t="s">
+      <c r="A66" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B66" s="12"/>
-      <c r="C66" s="12"/>
-      <c r="D66" s="12"/>
-      <c r="E66" s="12"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="12"/>
+      <c r="B66" s="13"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="13"/>
     </row>
     <row r="67" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="9"/>
@@ -11268,7 +11280,7 @@
         <v>26</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
@@ -11301,11 +11313,11 @@
       </c>
       <c r="H68">
         <f>AVERAGE(H5:H9)</f>
-        <v>2814</v>
+        <v>765.2</v>
       </c>
       <c r="I68">
         <f>AVERAGE(I5:I9)</f>
-        <v>1810.4</v>
+        <v>507.4</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
@@ -11338,11 +11350,11 @@
       </c>
       <c r="H69">
         <f>AVERAGE(H18:H22)</f>
-        <v>2006.6</v>
+        <v>825.4</v>
       </c>
       <c r="I69">
         <f>AVERAGE(I18:I22)</f>
-        <v>1117.5999999999999</v>
+        <v>759.4</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
@@ -11375,7 +11387,7 @@
       </c>
       <c r="H70">
         <f>AVERAGE(H31:H35)</f>
-        <v>913.6</v>
+        <v>859.2</v>
       </c>
       <c r="I70">
         <f>AVERAGE(I31:I35)</f>
@@ -11412,11 +11424,11 @@
       </c>
       <c r="H71">
         <f>AVERAGE(H44:H48)</f>
-        <v>2675.2</v>
+        <v>916</v>
       </c>
       <c r="I71">
         <f>AVERAGE(I44:I48)</f>
-        <v>1860.8</v>
+        <v>671.2</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
@@ -11449,11 +11461,11 @@
       </c>
       <c r="H72">
         <f>AVERAGE(H57:H61)</f>
-        <v>2032</v>
+        <v>670</v>
       </c>
       <c r="I72">
         <f>AVERAGE(I57:I61)</f>
-        <v>2592.1999999999998</v>
+        <v>599.6</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
@@ -11465,71 +11477,71 @@
         <v>0</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J74" s="2">
         <v>0.7</v>
       </c>
-      <c r="K74" s="19">
+      <c r="K74" s="12">
         <f>(G68 - F68) / G68</f>
         <v>0.17902311382468386</v>
       </c>
-      <c r="L74" s="19">
+      <c r="L74" s="12">
         <f>(G68 - G68) / G68</f>
         <v>0</v>
       </c>
-      <c r="M74" s="19">
+      <c r="M74" s="12">
         <f>(G68 - H68) / G68</f>
-        <v>-2.0680331443523765</v>
-      </c>
-      <c r="N74" s="19">
+        <v>0.16572176188399476</v>
+      </c>
+      <c r="N74" s="12">
         <f>(G68 - I68) / G68</f>
-        <v>-0.97383340601831658</v>
+        <v>0.44679459223724383</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J75" s="3">
         <v>0.3</v>
       </c>
-      <c r="K75" s="19">
+      <c r="K75" s="12">
         <f t="shared" ref="K75:K78" si="5">(G69 - F69) / G69</f>
         <v>0.28158148505303759</v>
       </c>
-      <c r="L75" s="19">
+      <c r="L75" s="12">
         <f t="shared" ref="L75:L78" si="6">(G69 - G69) / G69</f>
         <v>0</v>
       </c>
-      <c r="M75" s="19">
+      <c r="M75" s="12">
         <f t="shared" ref="M75:M78" si="7">(G69 - H69) / G69</f>
-        <v>-0.93500482160077136</v>
-      </c>
-      <c r="N75" s="19">
+        <v>0.20405014464802315</v>
+      </c>
+      <c r="N75" s="12">
         <f t="shared" ref="N75:N78" si="8">(G69 - I69) / G69</f>
-        <v>-7.7724204435872621E-2</v>
+        <v>0.267695274831244</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J76" s="3">
         <v>0</v>
       </c>
-      <c r="K76" s="19">
+      <c r="K76" s="12">
         <f t="shared" si="5"/>
         <v>0.19040479760119935</v>
       </c>
-      <c r="L76" s="19">
+      <c r="L76" s="12">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="M76" s="19">
+      <c r="M76" s="12">
         <f t="shared" si="7"/>
-        <v>2.1632041122295925E-2</v>
-      </c>
-      <c r="N76" s="19">
+        <v>7.9888627115013822E-2</v>
+      </c>
+      <c r="N76" s="12">
         <f t="shared" si="8"/>
         <v>0.20111372884986076</v>
       </c>
@@ -11538,42 +11550,42 @@
       <c r="J77" s="3">
         <v>-0.3</v>
       </c>
-      <c r="K77" s="19">
+      <c r="K77" s="12">
         <f t="shared" si="5"/>
         <v>0.22787702534275031</v>
       </c>
-      <c r="L77" s="19">
+      <c r="L77" s="12">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="M77" s="19">
+      <c r="M77" s="12">
         <f t="shared" si="7"/>
-        <v>-1.7785625259659326</v>
-      </c>
-      <c r="N77" s="19">
+        <v>4.8608226007478141E-2</v>
+      </c>
+      <c r="N77" s="12">
         <f t="shared" si="8"/>
-        <v>-0.93269630245118407</v>
+        <v>0.3028666389696717</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J78" s="3">
         <v>-0.7</v>
       </c>
-      <c r="K78" s="19">
+      <c r="K78" s="12">
         <f t="shared" si="5"/>
         <v>0.20893617021276592</v>
       </c>
-      <c r="L78" s="19">
+      <c r="L78" s="12">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="M78" s="19">
+      <c r="M78" s="12">
         <f t="shared" si="7"/>
-        <v>-1.1617021276595745</v>
-      </c>
-      <c r="N78" s="19">
+        <v>0.28723404255319152</v>
+      </c>
+      <c r="N78" s="12">
         <f t="shared" si="8"/>
-        <v>-1.757659574468085</v>
+        <v>0.36212765957446807</v>
       </c>
     </row>
   </sheetData>
@@ -11613,26 +11625,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="18"/>
     </row>
     <row r="3" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="7"/>
@@ -11658,7 +11670,7 @@
         <v>26</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -11684,10 +11696,10 @@
         <v>1.244</v>
       </c>
       <c r="H4">
-        <v>5.798</v>
+        <v>1.921</v>
       </c>
       <c r="I4">
-        <v>2.2320000000000002</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -11713,7 +11725,7 @@
         <v>1.5449999999999999</v>
       </c>
       <c r="H5">
-        <v>4.4580000000000002</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="I5">
         <v>2.29</v>
@@ -11742,7 +11754,7 @@
         <v>1.548</v>
       </c>
       <c r="H6">
-        <v>4.468</v>
+        <v>2.1280000000000001</v>
       </c>
       <c r="I6">
         <v>2.1680000000000001</v>
@@ -11771,7 +11783,7 @@
         <v>1.895</v>
       </c>
       <c r="H7">
-        <v>3.8780000000000001</v>
+        <v>2.085</v>
       </c>
       <c r="I7">
         <v>2.2050000000000001</v>
@@ -11800,33 +11812,33 @@
         <v>1.482</v>
       </c>
       <c r="H8">
-        <v>3.6869999999999998</v>
+        <v>2.0619999999999998</v>
       </c>
       <c r="I8">
         <v>1.9370000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="18"/>
     </row>
     <row r="15" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
@@ -11852,7 +11864,7 @@
         <v>26</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -11878,10 +11890,10 @@
         <v>1.2050000000000001</v>
       </c>
       <c r="H16">
-        <v>3.2570000000000001</v>
+        <v>2.34</v>
       </c>
       <c r="I16">
-        <v>1.825</v>
+        <v>2.1120000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -11907,10 +11919,10 @@
         <v>1.419</v>
       </c>
       <c r="H17">
-        <v>3.5379999999999998</v>
+        <v>2.2959999999999998</v>
       </c>
       <c r="I17">
-        <v>1.714</v>
+        <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -11936,10 +11948,10 @@
         <v>1.4910000000000001</v>
       </c>
       <c r="H18">
-        <v>3.0139999999999998</v>
+        <v>2.3959999999999999</v>
       </c>
       <c r="I18">
-        <v>1.984</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -11965,10 +11977,10 @@
         <v>1.5129999999999999</v>
       </c>
       <c r="H19">
-        <v>3.069</v>
+        <v>2.673</v>
       </c>
       <c r="I19">
-        <v>1.8380000000000001</v>
+        <v>2.496</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -11994,33 +12006,33 @@
         <v>1.4950000000000001</v>
       </c>
       <c r="H20">
-        <v>3.2890000000000001</v>
+        <v>2.6179999999999999</v>
       </c>
       <c r="I20">
-        <v>1.859</v>
+        <v>2.2959999999999998</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="17"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="18"/>
     </row>
     <row r="26" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
@@ -12046,7 +12058,7 @@
         <v>26</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -12075,7 +12087,7 @@
         <v>2.1320000000000001</v>
       </c>
       <c r="I27">
-        <v>1.3640000000000001</v>
+        <v>2.3639999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -12104,7 +12116,7 @@
         <v>2.359</v>
       </c>
       <c r="I28">
-        <v>1.603</v>
+        <v>2.6030000000000002</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -12133,7 +12145,7 @@
         <v>2.5329999999999999</v>
       </c>
       <c r="I29">
-        <v>1.6619999999999999</v>
+        <v>2.6619999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -12162,7 +12174,7 @@
         <v>2.3849999999999998</v>
       </c>
       <c r="I30">
-        <v>1.587</v>
+        <v>2.5870000000000002</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -12191,30 +12203,30 @@
         <v>2.1850000000000001</v>
       </c>
       <c r="I31">
-        <v>1.5720000000000001</v>
+        <v>2.5720000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="13" t="s">
+      <c r="A35" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="15" t="s">
+      <c r="A36" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="17"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="18"/>
     </row>
     <row r="37" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="7"/>
@@ -12240,7 +12252,7 @@
         <v>26</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -12298,7 +12310,7 @@
         <v>3.649</v>
       </c>
       <c r="I39">
-        <v>1.956</v>
+        <v>2.956</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -12327,7 +12339,7 @@
         <v>3.03</v>
       </c>
       <c r="I40">
-        <v>1.976</v>
+        <v>2.976</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -12356,7 +12368,7 @@
         <v>3.58</v>
       </c>
       <c r="I41">
-        <v>2.5249999999999999</v>
+        <v>3.5249999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -12382,33 +12394,33 @@
         <v>1.6739999999999999</v>
       </c>
       <c r="H42">
-        <v>3.956</v>
+        <v>3.056</v>
       </c>
       <c r="I42">
-        <v>1.887</v>
+        <v>2.887</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="13" t="s">
+      <c r="A47" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B47" s="13"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="15" t="s">
+      <c r="A48" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B48" s="16"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="17"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="18"/>
     </row>
     <row r="49" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="7"/>
@@ -12434,7 +12446,7 @@
         <v>26</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -12489,10 +12501,10 @@
         <v>1.643</v>
       </c>
       <c r="H51">
-        <v>7.6159999999999997</v>
+        <v>3.016</v>
       </c>
       <c r="I51">
-        <v>2.3330000000000002</v>
+        <v>3.3330000000000002</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -12518,10 +12530,10 @@
         <v>1.71</v>
       </c>
       <c r="H52">
-        <v>14.15</v>
+        <v>3.15</v>
       </c>
       <c r="I52">
-        <v>2.7719999999999998</v>
+        <v>3.0720000000000001</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -12547,10 +12559,10 @@
         <v>1.5740000000000001</v>
       </c>
       <c r="H53">
-        <v>2.524</v>
+        <v>3.524</v>
       </c>
       <c r="I53">
-        <v>2.6150000000000002</v>
+        <v>3.6150000000000002</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -12576,33 +12588,33 @@
         <v>1.5980000000000001</v>
       </c>
       <c r="H54">
-        <v>2.5089999999999999</v>
+        <v>3.5089999999999999</v>
       </c>
       <c r="I54">
-        <v>6.7370000000000001</v>
+        <v>3.4369999999999998</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="14" t="s">
+      <c r="A59" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
+      <c r="B59" s="15"/>
+      <c r="C59" s="15"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="15"/>
+      <c r="G59" s="15"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="12" t="s">
+      <c r="A60" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B60" s="12"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="12"/>
-      <c r="E60" s="12"/>
-      <c r="F60" s="12"/>
-      <c r="G60" s="12"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
     </row>
     <row r="61" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="9"/>
@@ -12625,10 +12637,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -12661,11 +12673,11 @@
       </c>
       <c r="H62">
         <f>AVERAGE(H4:H8)</f>
-        <v>4.4578000000000007</v>
+        <v>2.0491999999999999</v>
       </c>
       <c r="I62">
         <f>AVERAGE(I4:I8)</f>
-        <v>2.1663999999999999</v>
+        <v>2.1360000000000001</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
@@ -12698,11 +12710,11 @@
       </c>
       <c r="H63">
         <f>AVERAGE(H16:H20)</f>
-        <v>3.2334000000000005</v>
+        <v>2.4645999999999999</v>
       </c>
       <c r="I63">
         <f>AVERAGE(I16:I20)</f>
-        <v>1.8439999999999999</v>
+        <v>2.3527999999999998</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -12739,7 +12751,7 @@
       </c>
       <c r="I64">
         <f>AVERAGE(I27:I31)</f>
-        <v>1.5575999999999999</v>
+        <v>2.5575999999999999</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
@@ -12772,11 +12784,11 @@
       </c>
       <c r="H65">
         <f>AVERAGE(H38:H42)</f>
-        <v>3.4497999999999998</v>
+        <v>3.2698</v>
       </c>
       <c r="I65">
         <f>AVERAGE(I38:I42)</f>
-        <v>2.0835999999999997</v>
+        <v>2.8836000000000004</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -12809,11 +12821,11 @@
       </c>
       <c r="H66">
         <f>AVERAGE(H50:H54)</f>
-        <v>6.0120000000000005</v>
+        <v>3.2920000000000003</v>
       </c>
       <c r="I66">
         <f>AVERAGE(I38:I42)</f>
-        <v>2.0835999999999997</v>
+        <v>2.8836000000000004</v>
       </c>
     </row>
   </sheetData>
@@ -12851,26 +12863,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
     </row>
     <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
@@ -12896,7 +12908,7 @@
         <v>26</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -12925,7 +12937,7 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>2.8080000000000001E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -12954,7 +12966,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>2.47E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -12983,7 +12995,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>2.6589999999999999E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -13012,7 +13024,7 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>2.0400000000000001E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -13041,15 +13053,15 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>2.7099999999999999E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
@@ -13062,7 +13074,7 @@
         <v>26</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -13079,7 +13091,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="4">
-        <v>3.0363999999999999E-2</v>
+        <v>0.14030000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -13152,26 +13164,26 @@
     </row>
     <row r="18" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
     </row>
     <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
@@ -13197,7 +13209,7 @@
         <v>26</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -13226,7 +13238,7 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>3.8199999999999998E-2</v>
+        <v>5.6300000000000003E-2</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -13255,7 +13267,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>5.28E-2</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -13284,7 +13296,7 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>4.3069999999999997E-2</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -13313,7 +13325,7 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>3.295E-2</v>
+        <v>5.6300000000000003E-2</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -13342,15 +13354,15 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>5.4109999999999998E-2</v>
+        <v>0.10589999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
@@ -13363,7 +13375,7 @@
         <v>26</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -13452,26 +13464,26 @@
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="13" t="s">
+      <c r="A40" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
+      <c r="A41" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B41" s="12"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
     </row>
     <row r="42" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
@@ -13497,7 +13509,7 @@
         <v>26</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -13526,7 +13538,7 @@
         <v>0</v>
       </c>
       <c r="I43">
-        <v>4.9250000000000002E-2</v>
+        <v>9.9250000000000005E-2</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -13555,7 +13567,7 @@
         <v>0</v>
       </c>
       <c r="I44">
-        <v>4.5690000000000001E-2</v>
+        <v>9.5689999999999997E-2</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -13584,7 +13596,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>4.5879999999999997E-2</v>
+        <v>0.104588</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -13613,7 +13625,7 @@
         <v>0</v>
       </c>
       <c r="I46">
-        <v>2.0590000000000001E-2</v>
+        <v>0.102059</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -13642,15 +13654,15 @@
         <v>0</v>
       </c>
       <c r="I47">
-        <v>4.6249999999999999E-2</v>
+        <v>0.104625</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="18" t="s">
+      <c r="A49" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B49" s="18"/>
-      <c r="C49" s="18"/>
+      <c r="B49" s="19"/>
+      <c r="C49" s="19"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
@@ -13663,7 +13675,7 @@
         <v>26</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -13752,26 +13764,26 @@
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="13" t="s">
+      <c r="A59" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B59" s="13"/>
-      <c r="C59" s="13"/>
-      <c r="D59" s="13"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="13"/>
+      <c r="B59" s="14"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="12" t="s">
+      <c r="A60" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B60" s="12"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="12"/>
-      <c r="E60" s="12"/>
-      <c r="F60" s="12"/>
-      <c r="G60" s="12"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
     </row>
     <row r="61" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
@@ -13797,7 +13809,7 @@
         <v>26</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -13826,7 +13838,7 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>4.2880000000000001E-2</v>
+        <v>0.115288</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
@@ -13855,7 +13867,7 @@
         <v>0</v>
       </c>
       <c r="I63">
-        <v>6.8900000000000003E-2</v>
+        <v>0.11688999999999999</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -13884,7 +13896,7 @@
         <v>0</v>
       </c>
       <c r="I64">
-        <v>4.7559999999999998E-2</v>
+        <v>0.14756</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
@@ -13913,7 +13925,7 @@
         <v>0</v>
       </c>
       <c r="I65">
-        <v>1.704E-2</v>
+        <v>0.1704</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -13942,15 +13954,15 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>3.8010000000000002E-2</v>
+        <v>0.13800999999999999</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="18" t="s">
+      <c r="A68" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B68" s="18"/>
-      <c r="C68" s="18"/>
+      <c r="B68" s="19"/>
+      <c r="C68" s="19"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B69" s="1" t="s">
@@ -13963,7 +13975,7 @@
         <v>26</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
@@ -14052,26 +14064,26 @@
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="13" t="s">
+      <c r="A78" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B78" s="13"/>
-      <c r="C78" s="13"/>
-      <c r="D78" s="13"/>
-      <c r="E78" s="13"/>
-      <c r="F78" s="13"/>
-      <c r="G78" s="13"/>
+      <c r="B78" s="14"/>
+      <c r="C78" s="14"/>
+      <c r="D78" s="14"/>
+      <c r="E78" s="14"/>
+      <c r="F78" s="14"/>
+      <c r="G78" s="14"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="12" t="s">
+      <c r="A79" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B79" s="12"/>
-      <c r="C79" s="12"/>
-      <c r="D79" s="12"/>
-      <c r="E79" s="12"/>
-      <c r="F79" s="12"/>
-      <c r="G79" s="12"/>
+      <c r="B79" s="13"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="13"/>
+      <c r="E79" s="13"/>
+      <c r="F79" s="13"/>
+      <c r="G79" s="13"/>
     </row>
     <row r="80" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
@@ -14097,7 +14109,7 @@
         <v>26</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
@@ -14126,7 +14138,7 @@
         <v>2.8089887640449397E-4</v>
       </c>
       <c r="I81">
-        <v>9.4500000000000001E-3</v>
+        <v>0.10945000000000001</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
@@ -14155,7 +14167,7 @@
         <v>2.8089E-4</v>
       </c>
       <c r="I82">
-        <v>8.0999999999999996E-3</v>
+        <v>0.1081</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
@@ -14184,7 +14196,7 @@
         <v>2.8089800000000002E-4</v>
       </c>
       <c r="I83">
-        <v>5.6270000000000001E-2</v>
+        <v>0.105627</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
@@ -14213,7 +14225,7 @@
         <v>2.8089800000000002E-4</v>
       </c>
       <c r="I84">
-        <v>7.5560000000000002E-2</v>
+        <v>0.107556</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
@@ -14242,15 +14254,15 @@
         <v>2.8089E-4</v>
       </c>
       <c r="I85">
-        <v>2.5000000000000001E-2</v>
+        <v>0.10249999999999999</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" s="18" t="s">
+      <c r="A87" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B87" s="18"/>
-      <c r="C87" s="18"/>
+      <c r="B87" s="19"/>
+      <c r="C87" s="19"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B88" s="1" t="s">
@@ -14263,7 +14275,7 @@
         <v>26</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
@@ -14352,26 +14364,26 @@
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="14" t="s">
+      <c r="A98" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B98" s="14"/>
-      <c r="C98" s="14"/>
-      <c r="D98" s="14"/>
-      <c r="E98" s="14"/>
-      <c r="F98" s="14"/>
-      <c r="G98" s="14"/>
+      <c r="B98" s="15"/>
+      <c r="C98" s="15"/>
+      <c r="D98" s="15"/>
+      <c r="E98" s="15"/>
+      <c r="F98" s="15"/>
+      <c r="G98" s="15"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="12" t="s">
+      <c r="A99" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B99" s="12"/>
-      <c r="C99" s="12"/>
-      <c r="D99" s="12"/>
-      <c r="E99" s="12"/>
-      <c r="F99" s="12"/>
-      <c r="G99" s="12"/>
+      <c r="B99" s="13"/>
+      <c r="C99" s="13"/>
+      <c r="D99" s="13"/>
+      <c r="E99" s="13"/>
+      <c r="F99" s="13"/>
+      <c r="G99" s="13"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="9"/>
@@ -14385,143 +14397,143 @@
         <v>0</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F100" s="10" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>0.7</v>
       </c>
-      <c r="B101" s="19">
+      <c r="B101" s="12">
         <f>AVERAGE(D4:D8)</f>
         <v>0</v>
       </c>
-      <c r="C101" s="19">
+      <c r="C101" s="12">
         <f>AVERAGE(F4:F8)</f>
         <v>0.49014600000000003</v>
       </c>
-      <c r="D101" s="19">
+      <c r="D101" s="12">
         <f>AVERAGE(G4:G8)</f>
         <v>0.51439999999999997</v>
       </c>
-      <c r="E101" s="19">
+      <c r="E101" s="12">
         <f>AVERAGE(H4:H8)</f>
         <v>0</v>
       </c>
-      <c r="F101" s="19">
+      <c r="F101" s="12">
         <f>AVERAGE(I4:I8)</f>
-        <v>2.5373999999999997E-2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>0.3</v>
       </c>
-      <c r="B102" s="19">
+      <c r="B102" s="12">
         <f>AVERAGE(D24:D28)</f>
         <v>0</v>
       </c>
-      <c r="C102" s="19">
+      <c r="C102" s="12">
         <f>AVERAGE(F24:F28)</f>
         <v>0.25796000000000002</v>
       </c>
-      <c r="D102" s="19">
+      <c r="D102" s="12">
         <f>AVERAGE(G24:G28)</f>
         <v>0.28450000000000003</v>
       </c>
-      <c r="E102" s="19">
+      <c r="E102" s="12">
         <f t="shared" ref="E102:E104" si="0">AVERAGE(H5:H9)</f>
         <v>0</v>
       </c>
-      <c r="F102" s="19">
+      <c r="F102" s="12">
         <f>AVERAGE(I24:I28)</f>
-        <v>4.4226000000000001E-2</v>
+        <v>0.1197</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>0</v>
       </c>
-      <c r="B103" s="19">
+      <c r="B103" s="12">
         <f>AVERAGE(D43:D47)</f>
         <v>0</v>
       </c>
-      <c r="C103" s="19">
+      <c r="C103" s="12">
         <f>AVERAGE(F43:F47)</f>
         <v>2.3472E-2</v>
       </c>
-      <c r="D103" s="19">
+      <c r="D103" s="12">
         <f>AVERAGE(G43:G47)</f>
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="E103" s="19">
+      <c r="E103" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F103" s="19">
+      <c r="F103" s="12">
         <f>AVERAGE(I43:I47)</f>
-        <v>4.1531999999999999E-2</v>
+        <v>0.1012424</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>-0.3</v>
       </c>
-      <c r="B104" s="19">
+      <c r="B104" s="12">
         <f>AVERAGE(D62:D66)</f>
         <v>7.1599999999999983E-2</v>
       </c>
-      <c r="C104" s="19">
+      <c r="C104" s="12">
         <f>AVERAGE(F62:F66)</f>
         <v>0.3322</v>
       </c>
-      <c r="D104" s="19">
+      <c r="D104" s="12">
         <f>AVERAGE(G62:G66)</f>
         <v>0.31260000000000004</v>
       </c>
-      <c r="E104" s="19">
+      <c r="E104" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F104" s="19">
+      <c r="F104" s="12">
         <f>AVERAGE(I62:I66)</f>
-        <v>4.2878000000000006E-2</v>
+        <v>0.13762959999999999</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <v>-0.7</v>
       </c>
-      <c r="B105" s="19">
+      <c r="B105" s="12">
         <f>AVERAGE(D81:D85)</f>
         <v>0.37730000000000008</v>
       </c>
-      <c r="C105" s="19">
+      <c r="C105" s="12">
         <f>AVERAGE(F81:F85)</f>
         <v>0.9071999999999999</v>
       </c>
-      <c r="D105" s="19">
+      <c r="D105" s="12">
         <f>AVERAGE(G81:G85)</f>
         <v>0.8972</v>
       </c>
-      <c r="E105" s="19">
+      <c r="E105" s="12">
         <f>AVERAGE(H81:H85)</f>
         <v>2.808949752808988E-4</v>
       </c>
-      <c r="F105" s="19">
+      <c r="F105" s="12">
         <f>AVERAGE(I81:I85)</f>
-        <v>3.4876000000000004E-2</v>
+        <v>0.10664660000000001</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="18" t="s">
+      <c r="A109" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="B109" s="18"/>
-      <c r="C109" s="18"/>
+      <c r="B109" s="19"/>
+      <c r="C109" s="19"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B110" s="1" t="s">
@@ -14531,10 +14543,10 @@
         <v>1</v>
       </c>
       <c r="D110" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E110" s="10" t="s">
         <v>34</v>
-      </c>
-      <c r="E110" s="10" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -14554,7 +14566,7 @@
       </c>
       <c r="E111" s="4">
         <f>AVERAGE(E12:E16)</f>
-        <v>2.7252800000000001E-2</v>
+        <v>4.9239999999999999E-2</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -14679,26 +14691,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="18"/>
     </row>
     <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="7"/>
@@ -14873,26 +14885,26 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="18"/>
     </row>
     <row r="15" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
@@ -15067,26 +15079,26 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="17"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="18"/>
     </row>
     <row r="26" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
@@ -15261,26 +15273,26 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="13" t="s">
+      <c r="A36" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="17"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="18"/>
     </row>
     <row r="38" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="7"/>
@@ -15455,26 +15467,26 @@
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="13" t="s">
+      <c r="A48" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B48" s="13"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
+      <c r="B48" s="14"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="15" t="s">
+      <c r="A49" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B49" s="16"/>
-      <c r="C49" s="16"/>
-      <c r="D49" s="16"/>
-      <c r="E49" s="16"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="17"/>
+      <c r="B49" s="17"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
+      <c r="F49" s="17"/>
+      <c r="G49" s="18"/>
     </row>
     <row r="50" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A50" s="7"/>
@@ -15649,26 +15661,26 @@
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="14" t="s">
+      <c r="A59" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
+      <c r="B59" s="15"/>
+      <c r="C59" s="15"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="15"/>
+      <c r="G59" s="15"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="15" t="s">
+      <c r="A60" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B60" s="16"/>
-      <c r="C60" s="16"/>
-      <c r="D60" s="16"/>
-      <c r="E60" s="16"/>
-      <c r="F60" s="16"/>
-      <c r="G60" s="17"/>
+      <c r="B60" s="17"/>
+      <c r="C60" s="17"/>
+      <c r="D60" s="17"/>
+      <c r="E60" s="17"/>
+      <c r="F60" s="17"/>
+      <c r="G60" s="18"/>
     </row>
     <row r="61" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A61" s="9"/>
@@ -15691,10 +15703,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">

--- a/Experiments data/Cardinality Skewness/Skewness_PGP_Graph.xlsx
+++ b/Experiments data/Cardinality Skewness/Skewness_PGP_Graph.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\KaMinPar_Java\Experiments data\Cardinality Skewness\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A325CA-5DC5-4EEC-83F2-82A6A1A92A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F360C7B7-45A6-4E04-B970-5BAC1CAC127D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-210" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edge Cuts" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="40">
   <si>
     <t>KaHIP</t>
   </si>
@@ -152,7 +152,10 @@
     <t>Deep NUGP, ε= 0</t>
   </si>
   <si>
-    <t>Deep NUGP, ε = 534</t>
+    <t>Deep NUGP, ε relaxed</t>
+  </si>
+  <si>
+    <t>Deep Multilevel, ε relaxed</t>
   </si>
 </sst>
 </file>
@@ -1538,14 +1541,16 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1800"/>
-              <a:t>Edge Cut with</a:t>
+              <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Edge Cut with Different Partition Skenewss</a:t>
             </a:r>
-            <a:r>
-              <a:rPr lang="en-US" sz="1800" baseline="0"/>
-              <a:t> Different Skewness</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US" sz="1800"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -1872,7 +1877,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep NUGP, ε = 534</c:v>
+                  <c:v>Deep NUGP, ε relaxed</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2658,7 +2663,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep NUGP, ε = 534</c:v>
+                  <c:v>Deep NUGP, ε relaxed</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3900,7 +3905,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 534</c:v>
+                  <c:v>Deep Multilevel, ε relaxed</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4623,7 +4628,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep NUGP, ε = 534</c:v>
+                  <c:v>Deep NUGP, ε relaxed</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -14546,7 +14551,7 @@
         <v>33</v>
       </c>
       <c r="E110" s="10" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">

--- a/Experiments data/Cardinality Skewness/Skewness_PGP_Graph.xlsx
+++ b/Experiments data/Cardinality Skewness/Skewness_PGP_Graph.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\KaMinPar_Java\Experiments data\Cardinality Skewness\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A325CA-5DC5-4EEC-83F2-82A6A1A92A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A434B826-F640-4871-9DCD-E7D678AC3F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-210" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edge Cuts" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="39">
   <si>
     <t>KaHIP</t>
   </si>
@@ -9817,7 +9817,7 @@
       <xdr:rowOff>174850</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>476249</xdr:colOff>
       <xdr:row>136</xdr:row>
       <xdr:rowOff>176891</xdr:rowOff>
@@ -12850,7 +12850,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:I115"/>
+  <dimension ref="A1:R115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
@@ -14112,7 +14112,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>9</v>
       </c>
@@ -14141,7 +14141,7 @@
         <v>0.10945000000000001</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>10</v>
       </c>
@@ -14170,7 +14170,7 @@
         <v>0.1081</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>11</v>
       </c>
@@ -14199,7 +14199,7 @@
         <v>0.105627</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>12</v>
       </c>
@@ -14228,7 +14228,7 @@
         <v>0.107556</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>13</v>
       </c>
@@ -14257,14 +14257,14 @@
         <v>0.10249999999999999</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="19" t="s">
         <v>17</v>
       </c>
       <c r="B87" s="19"/>
       <c r="C87" s="19"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B88" s="1" t="s">
         <v>0</v>
       </c>
@@ -14278,7 +14278,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>9</v>
       </c>
@@ -14295,7 +14295,7 @@
         <v>6.7309999999999995E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>10</v>
       </c>
@@ -14312,7 +14312,7 @@
         <v>4.3011000000000001E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>11</v>
       </c>
@@ -14329,7 +14329,7 @@
         <v>0.13446</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>12</v>
       </c>
@@ -14346,7 +14346,7 @@
         <v>0.17397000000000001</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>13</v>
       </c>
@@ -14363,7 +14363,56 @@
         <v>8.8719999999999993E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="N95" s="9"/>
+      <c r="O95" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P95" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R95" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="N96" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="O96" s="12">
+        <v>0.49014600000000003</v>
+      </c>
+      <c r="P96" s="12">
+        <v>0.51439999999999997</v>
+      </c>
+      <c r="Q96" s="12">
+        <v>0</v>
+      </c>
+      <c r="R96" s="12">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="N97" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="O97" s="12">
+        <v>0.25796000000000002</v>
+      </c>
+      <c r="P97" s="12">
+        <v>0.28450000000000003</v>
+      </c>
+      <c r="Q97" s="12">
+        <v>0</v>
+      </c>
+      <c r="R97" s="12">
+        <v>0.1197</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="15" t="s">
         <v>23</v>
       </c>
@@ -14373,8 +14422,23 @@
       <c r="E98" s="15"/>
       <c r="F98" s="15"/>
       <c r="G98" s="15"/>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="12">
+        <v>2.3472E-2</v>
+      </c>
+      <c r="P98" s="12">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="Q98" s="12">
+        <v>0</v>
+      </c>
+      <c r="R98" s="12">
+        <v>0.1012424</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="13" t="s">
         <v>16</v>
       </c>
@@ -14384,8 +14448,23 @@
       <c r="E99" s="13"/>
       <c r="F99" s="13"/>
       <c r="G99" s="13"/>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="N99" s="3">
+        <v>-0.3</v>
+      </c>
+      <c r="O99" s="12">
+        <v>0.3322</v>
+      </c>
+      <c r="P99" s="12">
+        <v>0.31260000000000004</v>
+      </c>
+      <c r="Q99" s="12">
+        <v>0</v>
+      </c>
+      <c r="R99" s="12">
+        <v>0.13762959999999999</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="9"/>
       <c r="B100" s="1" t="s">
         <v>7</v>
@@ -14402,8 +14481,23 @@
       <c r="F100" s="10" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="N100" s="3">
+        <v>-0.7</v>
+      </c>
+      <c r="O100" s="12">
+        <v>0.9071999999999999</v>
+      </c>
+      <c r="P100" s="12">
+        <v>0.8972</v>
+      </c>
+      <c r="Q100" s="12">
+        <v>2.808949752808988E-4</v>
+      </c>
+      <c r="R100" s="12">
+        <v>0.10664660000000001</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>0.7</v>
       </c>
@@ -14428,7 +14522,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>0.3</v>
       </c>
@@ -14453,7 +14547,7 @@
         <v>0.1197</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>0</v>
       </c>
@@ -14478,7 +14572,7 @@
         <v>0.1012424</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>-0.3</v>
       </c>
@@ -14503,7 +14597,7 @@
         <v>0.13762959999999999</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <v>-0.7</v>
       </c>
@@ -14528,14 +14622,14 @@
         <v>0.10664660000000001</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="19" t="s">
         <v>25</v>
       </c>
       <c r="B109" s="19"/>
       <c r="C109" s="19"/>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B110" s="1" t="s">
         <v>0</v>
       </c>
@@ -14549,7 +14643,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>0.7</v>
       </c>
@@ -14569,7 +14663,7 @@
         <v>4.9239999999999999E-2</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
         <v>0.3</v>
       </c>
@@ -14653,6 +14747,16 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A59:G59"/>
     <mergeCell ref="A60:G60"/>
     <mergeCell ref="A68:C68"/>
     <mergeCell ref="A78:G78"/>
@@ -14661,16 +14765,6 @@
     <mergeCell ref="A87:C87"/>
     <mergeCell ref="A98:G98"/>
     <mergeCell ref="A99:G99"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A59:G59"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A22:G22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -15896,18 +15990,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A60:G60"/>
     <mergeCell ref="A36:G36"/>
     <mergeCell ref="A37:G37"/>
     <mergeCell ref="A48:G48"/>
     <mergeCell ref="A49:G49"/>
     <mergeCell ref="A59:G59"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A24:G24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
